--- a/data/Wine Recommended Order.xlsx
+++ b/data/Wine Recommended Order.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S147"/>
+  <dimension ref="A1:S145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7097,107 +7097,107 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Apothic Crush 750ml</t>
+          <t>Woodbridge Cab Sauv 1.5L</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>085000023488</t>
+          <t>086003813854</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="F109" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="G109" t="n">
-        <v>27</v>
+        <v>-12</v>
       </c>
       <c r="H109" t="n">
-        <v>16</v>
+        <v>22.8</v>
       </c>
       <c r="I109" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="J109" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K109" t="n">
         <v>12</v>
       </c>
       <c r="L109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M109" t="n">
-        <v>6.2</v>
+        <v>11.31</v>
       </c>
       <c r="N109" t="n">
-        <v>74</v>
+        <v>136</v>
       </c>
       <c r="O109" t="n">
-        <v>52</v>
-      </c>
-      <c r="Q109" t="inlineStr"/>
-      <c r="R109" t="inlineStr">
-        <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>ON AD - Sunday special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($74 to next deal) - confirm</t>
+          <t>Overstocked (10 wks on hand) - confirm before buying more; Seasonal - last year ~23/wk vs 10 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Barkan Sauvignon Blanc 750ml</t>
+          <t>Apothic Crush 750ml</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>087752008850</t>
+          <t>085000023488</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Sauvignon Blanc</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>12</v>
+        <v>140</v>
       </c>
       <c r="F110" t="n">
-        <v>10.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G110" t="n">
-        <v>-32</v>
+        <v>27</v>
       </c>
       <c r="H110" t="n">
-        <v>0.5</v>
+        <v>16</v>
       </c>
       <c r="I110" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J110" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="K110" t="n">
         <v>12</v>
@@ -7206,61 +7206,61 @@
         <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="N110" t="n">
-        <v>120</v>
+        <v>74</v>
       </c>
       <c r="O110" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="Q110" t="inlineStr"/>
       <c r="R110" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Apr, Jul, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($120 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($74 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Barefoot Pear Moscato 750ml</t>
+          <t>Barkan Sauvignon Blanc 750ml</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>085000037607</t>
+          <t>087752008850</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Sauvignon Blanc</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="F111" t="n">
-        <v>10.9</v>
+        <v>10.3</v>
       </c>
       <c r="G111" t="n">
-        <v>42</v>
+        <v>-32</v>
       </c>
       <c r="H111" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I111" t="n">
         <v>2</v>
-      </c>
-      <c r="I111" t="n">
-        <v>1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -7272,40 +7272,40 @@
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>4.32</v>
+        <v>10</v>
       </c>
       <c r="N111" t="n">
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="O111" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="Q111" t="inlineStr"/>
       <c r="R111" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, Apr, Jul, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($52 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($120 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Barefoot Chardonnay 750ml</t>
+          <t>Barefoot Pear Moscato 750ml</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>018341751055</t>
+          <t>085000037607</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -7314,22 +7314,22 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>129</v>
+        <v>66</v>
       </c>
       <c r="F112" t="n">
-        <v>11.3</v>
+        <v>10.9</v>
       </c>
       <c r="G112" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="H112" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="I112" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J112" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K112" t="n">
         <v>12</v>
@@ -7338,13 +7338,13 @@
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>4.4</v>
+        <v>4.32</v>
       </c>
       <c r="N112" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O112" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q112" t="inlineStr"/>
       <c r="R112" t="inlineStr">
@@ -7354,42 +7354,42 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($53 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($52 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Underwood Rose Bubbles NA 355ml</t>
+          <t>Barefoot Chardonnay 750ml</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>856036001692</t>
+          <t>018341751055</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Sparkling</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>43</v>
+        <v>129</v>
       </c>
       <c r="F113" t="n">
-        <v>11.5</v>
+        <v>11.3</v>
       </c>
       <c r="G113" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="I113" t="n">
         <v>5</v>
@@ -7398,46 +7398,46 @@
         <v>4</v>
       </c>
       <c r="K113" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="L113" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M113" t="n">
         <v>4.4</v>
       </c>
       <c r="N113" t="n">
-        <v>264</v>
+        <v>53</v>
       </c>
       <c r="O113" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="Q113" t="inlineStr"/>
       <c r="R113" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug, Oct) - stock up ~26wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($264 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($53 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Underwood Pinot Gris 375ml</t>
+          <t>Underwood Rose Bubbles NA 355ml</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>856036001067</t>
+          <t>856036001692</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Pinot Grigio/Gris</t>
+          <t>Sparkling</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -7446,34 +7446,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>89</v>
+        <v>43</v>
       </c>
       <c r="F114" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="G114" t="n">
-        <v>-21</v>
+        <v>9</v>
       </c>
       <c r="H114" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="I114" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J114" t="n">
         <v>4</v>
       </c>
       <c r="K114" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="L114" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M114" t="n">
-        <v>4.39</v>
+        <v>4.4</v>
       </c>
       <c r="N114" t="n">
-        <v>527</v>
+        <v>264</v>
       </c>
       <c r="O114" t="n">
         <v>32</v>
@@ -7486,24 +7486,24 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($527 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($264 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Boen Russian River Pinot Noir 750ml</t>
+          <t>Underwood Pinot Gris 375ml</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>856184006211</t>
+          <t>856036001067</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Pinot Grigio/Gris</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -7512,85 +7512,85 @@
         </is>
       </c>
       <c r="E115" t="n">
+        <v>89</v>
+      </c>
+      <c r="F115" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="G115" t="n">
+        <v>-21</v>
+      </c>
+      <c r="H115" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I115" t="n">
         <v>6</v>
       </c>
-      <c r="F115" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="G115" t="n">
-        <v>0</v>
-      </c>
-      <c r="H115" t="n">
-        <v>2</v>
-      </c>
-      <c r="I115" t="n">
-        <v>2</v>
-      </c>
       <c r="J115" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K115" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="L115" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M115" t="n">
-        <v>21.33</v>
+        <v>4.39</v>
       </c>
       <c r="N115" t="n">
-        <v>256</v>
+        <v>527</v>
       </c>
       <c r="O115" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="Q115" t="inlineStr"/>
       <c r="R115" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug, Oct) - stock up ~26wks to next deal</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($256 to next deal) - confirm; Seasonal - last year ~2/wk vs 0 now, buy ahead?</t>
+          <t>Buy-month stock-up ($527 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Line 39 Pinot Grigio 750ml</t>
+          <t>Boen Russian River Pinot Noir 750ml</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>898756001569</t>
+          <t>856184006211</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Pinot Grigio/Gris</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F116" t="n">
         <v>12.9</v>
       </c>
       <c r="G116" t="n">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -7602,58 +7602,58 @@
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>6.13</v>
+        <v>21.33</v>
       </c>
       <c r="N116" t="n">
-        <v>74</v>
+        <v>256</v>
       </c>
       <c r="O116" t="n">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="Q116" t="inlineStr"/>
       <c r="R116" t="inlineStr">
         <is>
-          <t>In buy-month (Sep, Oct) - stock up ~48wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($74 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($256 to next deal) - confirm; Seasonal - last year ~2/wk vs 0 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Daily's Strawberry RTD Frozen 10oz</t>
+          <t>Line 39 Pinot Grigio 750ml</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>074806184202</t>
+          <t>898756001569</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Pinot Grigio/Gris</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>211</v>
+        <v>3</v>
       </c>
       <c r="F117" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="G117" t="n">
-        <v>-42</v>
+        <v>-25</v>
       </c>
       <c r="H117" t="n">
-        <v>13.8</v>
+        <v>0.2</v>
       </c>
       <c r="I117" t="n">
         <v>1</v>
@@ -7662,112 +7662,112 @@
         <v>0</v>
       </c>
       <c r="K117" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="L117" t="n">
         <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>1.43</v>
+        <v>6.13</v>
       </c>
       <c r="N117" t="n">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="O117" t="n">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="Q117" t="inlineStr"/>
       <c r="R117" t="inlineStr">
         <is>
-          <t>In buy-month (Sep, Oct, Nov, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Sep, Oct) - stock up ~48wks to next deal</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($34 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($74 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Prati by Louis Martini Cabernet Sauvignon 750ml</t>
+          <t>Daily's Strawberry RTD Frozen 10oz</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>085000011638</t>
+          <t>074806184202</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>173</v>
+        <v>211</v>
       </c>
       <c r="F118" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="G118" t="n">
-        <v>7</v>
+        <v>-42</v>
       </c>
       <c r="H118" t="n">
-        <v>20.2</v>
+        <v>13.8</v>
       </c>
       <c r="I118" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J118" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>228</v>
+        <v>24</v>
       </c>
       <c r="L118" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>11.89</v>
+        <v>1.43</v>
       </c>
       <c r="N118" t="n">
-        <v>2711</v>
+        <v>34</v>
       </c>
       <c r="O118" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="Q118" t="inlineStr"/>
       <c r="R118" t="inlineStr">
         <is>
-          <t>In buy-month (May, Jul, Oct) - stock up ~30wks to next deal</t>
+          <t>In buy-month (Sep, Oct, Nov, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($2,711 to next deal) - confirm; Seasonal - last year ~20/wk vs 13 now, buy ahead?</t>
+          <t>Buy-month stock-up ($34 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Barefoot Strawberry Moscato 750ml</t>
+          <t>Prati by Louis Martini Cabernet Sauvignon 750ml</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>085000029015</t>
+          <t>085000011638</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -7776,82 +7776,82 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="F119" t="n">
-        <v>13.8</v>
+        <v>13.2</v>
       </c>
       <c r="G119" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H119" t="n">
-        <v>13.5</v>
+        <v>20.2</v>
       </c>
       <c r="I119" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="J119" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K119" t="n">
-        <v>12</v>
+        <v>228</v>
       </c>
       <c r="L119" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="M119" t="n">
-        <v>4.34</v>
+        <v>11.89</v>
       </c>
       <c r="N119" t="n">
-        <v>52</v>
+        <v>2711</v>
       </c>
       <c r="O119" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="Q119" t="inlineStr"/>
       <c r="R119" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (May, Jul, Oct) - stock up ~30wks to next deal</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($52 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($2,711 to next deal) - confirm; Seasonal - last year ~20/wk vs 13 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>90+ Cellars Cab Sauv California Lot 225 750ml</t>
+          <t>Barefoot Strawberry Moscato 750ml</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>894655001716</t>
+          <t>085000029015</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Bellboy Corporation</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>550</v>
+        <v>158</v>
       </c>
       <c r="F120" t="n">
-        <v>14</v>
+        <v>13.8</v>
       </c>
       <c r="G120" t="n">
         <v>4</v>
       </c>
       <c r="H120" t="n">
-        <v>52</v>
+        <v>13.5</v>
       </c>
       <c r="I120" t="n">
         <v>2</v>
@@ -7866,23 +7866,23 @@
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>6.6</v>
+        <v>4.34</v>
       </c>
       <c r="N120" t="n">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="O120" t="n">
-        <v>59</v>
-      </c>
-      <c r="Q120" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R120" t="inlineStr"/>
+        <v>46</v>
+      </c>
+      <c r="Q120" t="inlineStr"/>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>In buy-month (Jan, Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+        </is>
+      </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>Overstocked (14 wks on hand) - confirm before buying more</t>
+          <t>Buy-month stock-up ($52 to next deal) - confirm</t>
         </is>
       </c>
     </row>
@@ -8615,107 +8615,107 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Bota Box Breeze Cabernet 3L Box</t>
+          <t>Ferrari Carano Chardonnay 750ml</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>082242018074</t>
+          <t>742651107195</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>18</v>
+        <v>123</v>
       </c>
       <c r="F132" t="n">
-        <v>19.3</v>
+        <v>20.3</v>
       </c>
       <c r="G132" t="n">
-        <v>-8</v>
+        <v>-34</v>
       </c>
       <c r="H132" t="n">
-        <v>0.8</v>
+        <v>10.2</v>
       </c>
       <c r="I132" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J132" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K132" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="L132" t="n">
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>14.66</v>
+        <v>13.8</v>
       </c>
       <c r="N132" t="n">
-        <v>44</v>
+        <v>166</v>
       </c>
       <c r="O132" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q132" t="inlineStr">
-        <is>
-          <t>ON AD - Sunday special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R132" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="Q132" t="inlineStr"/>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>In buy-month (Feb, Mar, Jun, Aug, Oct, Nov) - stock up ~4wks to next deal</t>
+        </is>
+      </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>Overstocked (19 wks on hand) - confirm before buying more</t>
+          <t>Buy-month stock-up ($166 to next deal) - confirm; Seasonal - last year ~10/wk vs 6 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Ferrari Carano Chardonnay 750ml</t>
+          <t>Decoy Red Wine 750ml</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>742651107195</t>
+          <t>669576019207</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>123</v>
+        <v>87</v>
       </c>
       <c r="F133" t="n">
-        <v>20.3</v>
+        <v>20.7</v>
       </c>
       <c r="G133" t="n">
-        <v>-34</v>
+        <v>-23</v>
       </c>
       <c r="H133" t="n">
-        <v>10.2</v>
+        <v>7</v>
       </c>
       <c r="I133" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J133" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K133" t="n">
         <v>12</v>
@@ -8724,64 +8724,64 @@
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>13.8</v>
+        <v>14.76</v>
       </c>
       <c r="N133" t="n">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="O133" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Q133" t="inlineStr"/>
       <c r="R133" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Mar, Jun, Aug, Oct, Nov) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($166 to next deal) - confirm; Seasonal - last year ~10/wk vs 6 now, buy ahead?</t>
+          <t>Buy-month stock-up ($177 to next deal) - confirm; Seasonal - last year ~7/wk vs 4 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Decoy Red Wine 750ml</t>
+          <t>Bartenura Moscato Rose 750ml</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>669576019207</t>
+          <t>087752013854</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Moscato</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>87</v>
+        <v>15</v>
       </c>
       <c r="F134" t="n">
-        <v>20.7</v>
+        <v>21.4</v>
       </c>
       <c r="G134" t="n">
-        <v>-23</v>
+        <v>125</v>
       </c>
       <c r="H134" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I134" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J134" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K134" t="n">
         <v>12</v>
@@ -8790,61 +8790,61 @@
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>14.76</v>
+        <v>13.05</v>
       </c>
       <c r="N134" t="n">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="O134" t="n">
-        <v>38</v>
+        <v>-4</v>
       </c>
       <c r="Q134" t="inlineStr"/>
       <c r="R134" t="inlineStr">
         <is>
-          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Feb, Apr, Jul, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($177 to next deal) - confirm; Seasonal - last year ~7/wk vs 4 now, buy ahead?</t>
+          <t>Margin looks off - check retail/cost; Buy-month stock-up ($157 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Bartenura Moscato Rose 750ml</t>
+          <t>Decoy Sonoma Pinot Noir 750ml</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>087752013854</t>
+          <t>669576019221</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Moscato</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>15</v>
+        <v>132</v>
       </c>
       <c r="F135" t="n">
-        <v>21.4</v>
+        <v>22.6</v>
       </c>
       <c r="G135" t="n">
-        <v>125</v>
+        <v>-39</v>
       </c>
       <c r="H135" t="n">
-        <v>1</v>
+        <v>10.2</v>
       </c>
       <c r="I135" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -8856,40 +8856,40 @@
         <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>13.05</v>
+        <v>12.92</v>
       </c>
       <c r="N135" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O135" t="n">
-        <v>-4</v>
+        <v>46</v>
       </c>
       <c r="Q135" t="inlineStr"/>
       <c r="R135" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Apr, Jul, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>Margin looks off - check retail/cost; Buy-month stock-up ($157 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($155 to next deal) - confirm; Seasonal - last year ~10/wk vs 6 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Decoy Sonoma Pinot Noir 750ml</t>
+          <t>Decoy Merlot 750ml</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>669576019221</t>
+          <t>669576019252</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Merlot</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -8898,19 +8898,19 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="F136" t="n">
-        <v>22.6</v>
+        <v>24</v>
       </c>
       <c r="G136" t="n">
-        <v>-39</v>
+        <v>6</v>
       </c>
       <c r="H136" t="n">
-        <v>10.2</v>
+        <v>6.8</v>
       </c>
       <c r="I136" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -8922,13 +8922,13 @@
         <v>1</v>
       </c>
       <c r="M136" t="n">
-        <v>12.92</v>
+        <v>13.34</v>
       </c>
       <c r="N136" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="O136" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q136" t="inlineStr"/>
       <c r="R136" t="inlineStr">
@@ -8938,24 +8938,24 @@
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($155 to next deal) - confirm; Seasonal - last year ~10/wk vs 6 now, buy ahead?</t>
+          <t>Buy-month stock-up ($160 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Decoy Merlot 750ml</t>
+          <t>Line 39 Cabernet 750ml</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>669576019252</t>
+          <t>898756001057</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Merlot</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -8964,82 +8964,82 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="F137" t="n">
-        <v>24</v>
+        <v>26.2</v>
       </c>
       <c r="G137" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H137" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="I137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
       </c>
       <c r="K137" t="n">
-        <v>12</v>
+        <v>132</v>
       </c>
       <c r="L137" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="M137" t="n">
-        <v>13.34</v>
+        <v>6.26</v>
       </c>
       <c r="N137" t="n">
-        <v>160</v>
+        <v>827</v>
       </c>
       <c r="O137" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="Q137" t="inlineStr"/>
       <c r="R137" t="inlineStr">
         <is>
-          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Sep, Oct) - stock up ~48wks to next deal</t>
         </is>
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($160 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($827 to next deal) - confirm; Seasonal - last year ~9/wk vs 6 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Line 39 Cabernet 750ml</t>
+          <t>Boen Tri Appellation Chardonnay 750ml</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>898756001057</t>
+          <t>856184006310</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>147</v>
+        <v>38</v>
       </c>
       <c r="F138" t="n">
-        <v>26.2</v>
+        <v>27.1</v>
       </c>
       <c r="G138" t="n">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="H138" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I138" t="n">
         <v>2</v>
@@ -9048,70 +9048,70 @@
         <v>0</v>
       </c>
       <c r="K138" t="n">
-        <v>132</v>
+        <v>12</v>
       </c>
       <c r="L138" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="M138" t="n">
-        <v>6.26</v>
+        <v>12.23</v>
       </c>
       <c r="N138" t="n">
-        <v>827</v>
+        <v>147</v>
       </c>
       <c r="O138" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="Q138" t="inlineStr"/>
       <c r="R138" t="inlineStr">
         <is>
-          <t>In buy-month (Sep, Oct) - stock up ~48wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($827 to next deal) - confirm; Seasonal - last year ~9/wk vs 6 now, buy ahead?</t>
+          <t>Buy-month stock-up ($147 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Boen Tri Appellation Chardonnay 750ml</t>
+          <t>Barefoot Merlot 750ml</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>856184006310</t>
+          <t>018341751109</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Merlot</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="F139" t="n">
-        <v>27.1</v>
+        <v>29.5</v>
       </c>
       <c r="G139" t="n">
-        <v>64</v>
+        <v>-27</v>
       </c>
       <c r="H139" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="I139" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J139" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K139" t="n">
         <v>12</v>
@@ -9120,40 +9120,40 @@
         <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>12.23</v>
+        <v>4.42</v>
       </c>
       <c r="N139" t="n">
-        <v>147</v>
+        <v>53</v>
       </c>
       <c r="O139" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="Q139" t="inlineStr"/>
       <c r="R139" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($147 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($53 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Barefoot Merlot 750ml</t>
+          <t>Barefoot Pinot Noir 750ml</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>018341751109</t>
+          <t>085000017074</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Merlot</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -9162,22 +9162,22 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="F140" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="G140" t="n">
-        <v>-27</v>
+        <v>-22</v>
       </c>
       <c r="H140" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="I140" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J140" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K140" t="n">
         <v>12</v>
@@ -9186,13 +9186,13 @@
         <v>1</v>
       </c>
       <c r="M140" t="n">
-        <v>4.42</v>
+        <v>4.32</v>
       </c>
       <c r="N140" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O140" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q140" t="inlineStr"/>
       <c r="R140" t="inlineStr">
@@ -9202,42 +9202,42 @@
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($53 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($52 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Barefoot Pinot Noir 750ml</t>
+          <t>Banshee Paso Cab 750ml</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>085000017074</t>
+          <t>853868006345</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="F141" t="n">
-        <v>29.6</v>
+        <v>30.9</v>
       </c>
       <c r="G141" t="n">
-        <v>-22</v>
+        <v>45</v>
       </c>
       <c r="H141" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="I141" t="n">
         <v>2</v>
@@ -9252,10 +9252,10 @@
         <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>4.32</v>
+        <v>13.97</v>
       </c>
       <c r="N141" t="n">
-        <v>52</v>
+        <v>168</v>
       </c>
       <c r="O141" t="n">
         <v>46</v>
@@ -9263,50 +9263,50 @@
       <c r="Q141" t="inlineStr"/>
       <c r="R141" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, Mar, Jun, Aug, Oct, Nov) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($52 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($168 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Banshee Paso Cab 750ml</t>
+          <t>Bartenura Pinot Grigio 750ml</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>853868006345</t>
+          <t>087752003435</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Pinot Grigio/Gris</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>101</v>
+        <v>54</v>
       </c>
       <c r="F142" t="n">
-        <v>30.9</v>
+        <v>33.1</v>
       </c>
       <c r="G142" t="n">
-        <v>45</v>
+        <v>91</v>
       </c>
       <c r="H142" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="I142" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -9318,61 +9318,61 @@
         <v>1</v>
       </c>
       <c r="M142" t="n">
-        <v>13.97</v>
+        <v>11.58</v>
       </c>
       <c r="N142" t="n">
-        <v>168</v>
+        <v>139</v>
       </c>
       <c r="O142" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="Q142" t="inlineStr"/>
       <c r="R142" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Mar, Jun, Aug, Oct, Nov) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Feb, Apr, Jul, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($168 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($139 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>90+ Cellars 2019 Lot 26 Barolo 750ml</t>
+          <t>Barkan Cabernet Sauvignon 750ml</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>894655001440</t>
+          <t>087752006108</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Other Reds</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Bellboy Corporation</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="F143" t="n">
-        <v>33.1</v>
+        <v>41.8</v>
       </c>
       <c r="G143" t="n">
-        <v>-15</v>
+        <v>-43</v>
       </c>
       <c r="H143" t="n">
-        <v>4.2</v>
+        <v>0.2</v>
       </c>
       <c r="I143" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -9384,61 +9384,61 @@
         <v>1</v>
       </c>
       <c r="M143" t="n">
-        <v>17.44</v>
+        <v>9.75</v>
       </c>
       <c r="N143" t="n">
-        <v>209</v>
+        <v>117</v>
       </c>
       <c r="O143" t="n">
-        <v>56</v>
-      </c>
-      <c r="Q143" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R143" t="inlineStr"/>
+        <v>39</v>
+      </c>
+      <c r="Q143" t="inlineStr"/>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>In buy-month (Feb, Apr, Jul, Oct, Dec) - stock up ~9wks to next deal</t>
+        </is>
+      </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>Overstocked (33 wks on hand) - confirm before buying more; Seasonal - last year ~4/wk vs 3 now, buy ahead?</t>
+          <t>Buy-month stock-up ($117 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Bartenura Pinot Grigio 750ml</t>
+          <t>Apothic Inferno 750ml</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>087752003435</t>
+          <t>085000024904</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Pinot Grigio/Gris</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>54</v>
+        <v>186</v>
       </c>
       <c r="F144" t="n">
-        <v>33.1</v>
+        <v>44.3</v>
       </c>
       <c r="G144" t="n">
-        <v>91</v>
+        <v>-14</v>
       </c>
       <c r="H144" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I144" t="n">
         <v>2</v>
-      </c>
-      <c r="I144" t="n">
-        <v>1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -9450,40 +9450,40 @@
         <v>1</v>
       </c>
       <c r="M144" t="n">
-        <v>11.58</v>
+        <v>8.42</v>
       </c>
       <c r="N144" t="n">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="O144" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="Q144" t="inlineStr"/>
       <c r="R144" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Apr, Jul, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($139 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($101 to next deal) - confirm; Seasonal - last year ~7/wk vs 4 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Barkan Cabernet Sauvignon 750ml</t>
+          <t>Rashi Claret 750ml</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>087752006108</t>
+          <t>087752008454</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -9492,16 +9492,16 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="F145" t="n">
-        <v>41.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G145" t="n">
-        <v>-43</v>
+        <v>200</v>
       </c>
       <c r="H145" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="I145" t="n">
         <v>1</v>
@@ -9516,13 +9516,13 @@
         <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>9.75</v>
+        <v>7.62</v>
       </c>
       <c r="N145" t="n">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="O145" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="Q145" t="inlineStr"/>
       <c r="R145" t="inlineStr">
@@ -9531,138 +9531,6 @@
         </is>
       </c>
       <c r="S145" t="inlineStr">
-        <is>
-          <t>Buy-month stock-up ($117 to next deal) - confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Apothic Inferno 750ml</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>085000024904</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Red Blends</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>Johnson Brothers - St. Paul</t>
-        </is>
-      </c>
-      <c r="E146" t="n">
-        <v>186</v>
-      </c>
-      <c r="F146" t="n">
-        <v>44.3</v>
-      </c>
-      <c r="G146" t="n">
-        <v>-14</v>
-      </c>
-      <c r="H146" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="I146" t="n">
-        <v>2</v>
-      </c>
-      <c r="J146" t="n">
-        <v>0</v>
-      </c>
-      <c r="K146" t="n">
-        <v>12</v>
-      </c>
-      <c r="L146" t="n">
-        <v>1</v>
-      </c>
-      <c r="M146" t="n">
-        <v>8.42</v>
-      </c>
-      <c r="N146" t="n">
-        <v>101</v>
-      </c>
-      <c r="O146" t="n">
-        <v>44</v>
-      </c>
-      <c r="Q146" t="inlineStr"/>
-      <c r="R146" t="inlineStr">
-        <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
-        </is>
-      </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>Buy-month stock-up ($101 to next deal) - confirm; Seasonal - last year ~7/wk vs 4 now, buy ahead?</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Rashi Claret 750ml</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>087752008454</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Red Blends</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
-        </is>
-      </c>
-      <c r="E147" t="n">
-        <v>82</v>
-      </c>
-      <c r="F147" t="n">
-        <v>87.90000000000001</v>
-      </c>
-      <c r="G147" t="n">
-        <v>200</v>
-      </c>
-      <c r="H147" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I147" t="n">
-        <v>1</v>
-      </c>
-      <c r="J147" t="n">
-        <v>0</v>
-      </c>
-      <c r="K147" t="n">
-        <v>12</v>
-      </c>
-      <c r="L147" t="n">
-        <v>1</v>
-      </c>
-      <c r="M147" t="n">
-        <v>7.62</v>
-      </c>
-      <c r="N147" t="n">
-        <v>91</v>
-      </c>
-      <c r="O147" t="n">
-        <v>34</v>
-      </c>
-      <c r="Q147" t="inlineStr"/>
-      <c r="R147" t="inlineStr">
-        <is>
-          <t>In buy-month (Feb, Apr, Jul, Oct, Dec) - stock up ~9wks to next deal</t>
-        </is>
-      </c>
-      <c r="S147" t="inlineStr">
         <is>
           <t>Buy-month stock-up ($91 to next deal) - confirm</t>
         </is>
@@ -9679,7 +9547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S95"/>
+  <dimension ref="A1:S93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13383,107 +13251,107 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Apothic Crush 750ml</t>
+          <t>Woodbridge Cab Sauv 1.5L</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>085000023488</t>
+          <t>086003813854</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="F57" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="G57" t="n">
-        <v>27</v>
+        <v>-12</v>
       </c>
       <c r="H57" t="n">
-        <v>16</v>
+        <v>22.8</v>
       </c>
       <c r="I57" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="J57" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
         <v>12</v>
       </c>
       <c r="L57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M57" t="n">
-        <v>6.2</v>
+        <v>11.31</v>
       </c>
       <c r="N57" t="n">
-        <v>74</v>
+        <v>136</v>
       </c>
       <c r="O57" t="n">
-        <v>52</v>
-      </c>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>ON AD - Sunday special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($74 to next deal) - confirm</t>
+          <t>Overstocked (10 wks on hand) - confirm before buying more; Seasonal - last year ~23/wk vs 10 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Barkan Sauvignon Blanc 750ml</t>
+          <t>Apothic Crush 750ml</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>087752008850</t>
+          <t>085000023488</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sauvignon Blanc</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>12</v>
+        <v>140</v>
       </c>
       <c r="F58" t="n">
-        <v>10.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G58" t="n">
-        <v>-32</v>
+        <v>27</v>
       </c>
       <c r="H58" t="n">
-        <v>0.5</v>
+        <v>16</v>
       </c>
       <c r="I58" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="K58" t="n">
         <v>12</v>
@@ -13492,61 +13360,61 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="N58" t="n">
-        <v>120</v>
+        <v>74</v>
       </c>
       <c r="O58" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Apr, Jul, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($120 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($74 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Barefoot Pear Moscato 750ml</t>
+          <t>Barkan Sauvignon Blanc 750ml</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>085000037607</t>
+          <t>087752008850</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Sauvignon Blanc</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="F59" t="n">
-        <v>10.9</v>
+        <v>10.3</v>
       </c>
       <c r="G59" t="n">
-        <v>42</v>
+        <v>-32</v>
       </c>
       <c r="H59" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I59" t="n">
         <v>2</v>
-      </c>
-      <c r="I59" t="n">
-        <v>1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -13558,40 +13426,40 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>4.32</v>
+        <v>10</v>
       </c>
       <c r="N59" t="n">
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="O59" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, Apr, Jul, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($52 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($120 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Barefoot Chardonnay 750ml</t>
+          <t>Barefoot Pear Moscato 750ml</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>018341751055</t>
+          <t>085000037607</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -13600,22 +13468,22 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>129</v>
+        <v>66</v>
       </c>
       <c r="F60" t="n">
-        <v>11.3</v>
+        <v>10.9</v>
       </c>
       <c r="G60" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="H60" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="I60" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
         <v>12</v>
@@ -13624,13 +13492,13 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>4.4</v>
+        <v>4.32</v>
       </c>
       <c r="N60" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O60" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr">
@@ -13640,42 +13508,42 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($53 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($52 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Underwood Rose Bubbles NA 355ml</t>
+          <t>Barefoot Chardonnay 750ml</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>856036001692</t>
+          <t>018341751055</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sparkling</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>43</v>
+        <v>129</v>
       </c>
       <c r="F61" t="n">
-        <v>11.5</v>
+        <v>11.3</v>
       </c>
       <c r="G61" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="I61" t="n">
         <v>5</v>
@@ -13684,46 +13552,46 @@
         <v>4</v>
       </c>
       <c r="K61" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="L61" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M61" t="n">
         <v>4.4</v>
       </c>
       <c r="N61" t="n">
-        <v>264</v>
+        <v>53</v>
       </c>
       <c r="O61" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug, Oct) - stock up ~26wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($264 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($53 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Underwood Pinot Gris 375ml</t>
+          <t>Underwood Rose Bubbles NA 355ml</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>856036001067</t>
+          <t>856036001692</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Pinot Grigio/Gris</t>
+          <t>Sparkling</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -13732,34 +13600,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>89</v>
+        <v>43</v>
       </c>
       <c r="F62" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="G62" t="n">
-        <v>-21</v>
+        <v>9</v>
       </c>
       <c r="H62" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J62" t="n">
         <v>4</v>
       </c>
       <c r="K62" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="L62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M62" t="n">
-        <v>4.39</v>
+        <v>4.4</v>
       </c>
       <c r="N62" t="n">
-        <v>527</v>
+        <v>264</v>
       </c>
       <c r="O62" t="n">
         <v>32</v>
@@ -13772,24 +13640,24 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($527 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($264 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Boen Russian River Pinot Noir 750ml</t>
+          <t>Underwood Pinot Gris 375ml</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>856184006211</t>
+          <t>856036001067</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Pinot Grigio/Gris</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -13798,85 +13666,85 @@
         </is>
       </c>
       <c r="E63" t="n">
+        <v>89</v>
+      </c>
+      <c r="F63" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-21</v>
+      </c>
+      <c r="H63" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I63" t="n">
         <v>6</v>
       </c>
-      <c r="F63" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="G63" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="n">
-        <v>2</v>
-      </c>
-      <c r="I63" t="n">
-        <v>2</v>
-      </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K63" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="L63" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M63" t="n">
-        <v>21.33</v>
+        <v>4.39</v>
       </c>
       <c r="N63" t="n">
-        <v>256</v>
+        <v>527</v>
       </c>
       <c r="O63" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug, Oct) - stock up ~26wks to next deal</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($256 to next deal) - confirm; Seasonal - last year ~2/wk vs 0 now, buy ahead?</t>
+          <t>Buy-month stock-up ($527 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Line 39 Pinot Grigio 750ml</t>
+          <t>Boen Russian River Pinot Noir 750ml</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>898756001569</t>
+          <t>856184006211</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Pinot Grigio/Gris</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>12.9</v>
       </c>
       <c r="G64" t="n">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -13888,58 +13756,58 @@
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>6.13</v>
+        <v>21.33</v>
       </c>
       <c r="N64" t="n">
-        <v>74</v>
+        <v>256</v>
       </c>
       <c r="O64" t="n">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr">
         <is>
-          <t>In buy-month (Sep, Oct) - stock up ~48wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($74 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($256 to next deal) - confirm; Seasonal - last year ~2/wk vs 0 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Daily's Strawberry RTD Frozen 10oz</t>
+          <t>Line 39 Pinot Grigio 750ml</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>074806184202</t>
+          <t>898756001569</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Pinot Grigio/Gris</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>211</v>
+        <v>3</v>
       </c>
       <c r="F65" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="G65" t="n">
-        <v>-42</v>
+        <v>-25</v>
       </c>
       <c r="H65" t="n">
-        <v>13.8</v>
+        <v>0.2</v>
       </c>
       <c r="I65" t="n">
         <v>1</v>
@@ -13948,112 +13816,112 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="L65" t="n">
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>1.43</v>
+        <v>6.13</v>
       </c>
       <c r="N65" t="n">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="O65" t="n">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr">
         <is>
-          <t>In buy-month (Sep, Oct, Nov, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Sep, Oct) - stock up ~48wks to next deal</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($34 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($74 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Prati by Louis Martini Cabernet Sauvignon 750ml</t>
+          <t>Daily's Strawberry RTD Frozen 10oz</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>085000011638</t>
+          <t>074806184202</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>173</v>
+        <v>211</v>
       </c>
       <c r="F66" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="G66" t="n">
-        <v>7</v>
+        <v>-42</v>
       </c>
       <c r="H66" t="n">
-        <v>20.2</v>
+        <v>13.8</v>
       </c>
       <c r="I66" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>228</v>
+        <v>24</v>
       </c>
       <c r="L66" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>11.89</v>
+        <v>1.43</v>
       </c>
       <c r="N66" t="n">
-        <v>2711</v>
+        <v>34</v>
       </c>
       <c r="O66" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr">
         <is>
-          <t>In buy-month (May, Jul, Oct) - stock up ~30wks to next deal</t>
+          <t>In buy-month (Sep, Oct, Nov, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($2,711 to next deal) - confirm; Seasonal - last year ~20/wk vs 13 now, buy ahead?</t>
+          <t>Buy-month stock-up ($34 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Barefoot Strawberry Moscato 750ml</t>
+          <t>Prati by Louis Martini Cabernet Sauvignon 750ml</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>085000029015</t>
+          <t>085000011638</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -14062,82 +13930,82 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="F67" t="n">
-        <v>13.8</v>
+        <v>13.2</v>
       </c>
       <c r="G67" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H67" t="n">
-        <v>13.5</v>
+        <v>20.2</v>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K67" t="n">
-        <v>12</v>
+        <v>228</v>
       </c>
       <c r="L67" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="M67" t="n">
-        <v>4.34</v>
+        <v>11.89</v>
       </c>
       <c r="N67" t="n">
-        <v>52</v>
+        <v>2711</v>
       </c>
       <c r="O67" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (May, Jul, Oct) - stock up ~30wks to next deal</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($52 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($2,711 to next deal) - confirm; Seasonal - last year ~20/wk vs 13 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>90+ Cellars Cab Sauv California Lot 225 750ml</t>
+          <t>Barefoot Strawberry Moscato 750ml</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>894655001716</t>
+          <t>085000029015</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Bellboy Corporation</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>550</v>
+        <v>158</v>
       </c>
       <c r="F68" t="n">
-        <v>14</v>
+        <v>13.8</v>
       </c>
       <c r="G68" t="n">
         <v>4</v>
       </c>
       <c r="H68" t="n">
-        <v>52</v>
+        <v>13.5</v>
       </c>
       <c r="I68" t="n">
         <v>2</v>
@@ -14152,23 +14020,23 @@
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>6.6</v>
+        <v>4.34</v>
       </c>
       <c r="N68" t="n">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="O68" t="n">
-        <v>59</v>
-      </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R68" t="inlineStr"/>
+        <v>46</v>
+      </c>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>In buy-month (Jan, Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+        </is>
+      </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>Overstocked (14 wks on hand) - confirm before buying more</t>
+          <t>Buy-month stock-up ($52 to next deal) - confirm</t>
         </is>
       </c>
     </row>
@@ -14901,107 +14769,107 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Bota Box Breeze Cabernet 3L Box</t>
+          <t>Ferrari Carano Chardonnay 750ml</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>082242018074</t>
+          <t>742651107195</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>18</v>
+        <v>123</v>
       </c>
       <c r="F80" t="n">
-        <v>19.3</v>
+        <v>20.3</v>
       </c>
       <c r="G80" t="n">
-        <v>-8</v>
+        <v>-34</v>
       </c>
       <c r="H80" t="n">
-        <v>0.8</v>
+        <v>10.2</v>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K80" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>14.66</v>
+        <v>13.8</v>
       </c>
       <c r="N80" t="n">
-        <v>44</v>
+        <v>166</v>
       </c>
       <c r="O80" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>ON AD - Sunday special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R80" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>In buy-month (Feb, Mar, Jun, Aug, Oct, Nov) - stock up ~4wks to next deal</t>
+        </is>
+      </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>Overstocked (19 wks on hand) - confirm before buying more</t>
+          <t>Buy-month stock-up ($166 to next deal) - confirm; Seasonal - last year ~10/wk vs 6 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Ferrari Carano Chardonnay 750ml</t>
+          <t>Decoy Red Wine 750ml</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>742651107195</t>
+          <t>669576019207</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>123</v>
+        <v>87</v>
       </c>
       <c r="F81" t="n">
-        <v>20.3</v>
+        <v>20.7</v>
       </c>
       <c r="G81" t="n">
-        <v>-34</v>
+        <v>-23</v>
       </c>
       <c r="H81" t="n">
-        <v>10.2</v>
+        <v>7</v>
       </c>
       <c r="I81" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J81" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K81" t="n">
         <v>12</v>
@@ -15010,64 +14878,64 @@
         <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>13.8</v>
+        <v>14.76</v>
       </c>
       <c r="N81" t="n">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="O81" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Mar, Jun, Aug, Oct, Nov) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($166 to next deal) - confirm; Seasonal - last year ~10/wk vs 6 now, buy ahead?</t>
+          <t>Buy-month stock-up ($177 to next deal) - confirm; Seasonal - last year ~7/wk vs 4 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Decoy Red Wine 750ml</t>
+          <t>Bartenura Moscato Rose 750ml</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>669576019207</t>
+          <t>087752013854</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Moscato</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>87</v>
+        <v>15</v>
       </c>
       <c r="F82" t="n">
-        <v>20.7</v>
+        <v>21.4</v>
       </c>
       <c r="G82" t="n">
-        <v>-23</v>
+        <v>125</v>
       </c>
       <c r="H82" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I82" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J82" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
         <v>12</v>
@@ -15076,61 +14944,61 @@
         <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>14.76</v>
+        <v>13.05</v>
       </c>
       <c r="N82" t="n">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="O82" t="n">
-        <v>38</v>
+        <v>-4</v>
       </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr">
         <is>
-          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Feb, Apr, Jul, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($177 to next deal) - confirm; Seasonal - last year ~7/wk vs 4 now, buy ahead?</t>
+          <t>Margin looks off - check retail/cost; Buy-month stock-up ($157 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Bartenura Moscato Rose 750ml</t>
+          <t>Decoy Sonoma Pinot Noir 750ml</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>087752013854</t>
+          <t>669576019221</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Moscato</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>15</v>
+        <v>132</v>
       </c>
       <c r="F83" t="n">
-        <v>21.4</v>
+        <v>22.6</v>
       </c>
       <c r="G83" t="n">
-        <v>125</v>
+        <v>-39</v>
       </c>
       <c r="H83" t="n">
-        <v>1</v>
+        <v>10.2</v>
       </c>
       <c r="I83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -15142,40 +15010,40 @@
         <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>13.05</v>
+        <v>12.92</v>
       </c>
       <c r="N83" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O83" t="n">
-        <v>-4</v>
+        <v>46</v>
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Apr, Jul, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>Margin looks off - check retail/cost; Buy-month stock-up ($157 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($155 to next deal) - confirm; Seasonal - last year ~10/wk vs 6 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Decoy Sonoma Pinot Noir 750ml</t>
+          <t>Decoy Merlot 750ml</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>669576019221</t>
+          <t>669576019252</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Merlot</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -15184,19 +15052,19 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="F84" t="n">
-        <v>22.6</v>
+        <v>24</v>
       </c>
       <c r="G84" t="n">
-        <v>-39</v>
+        <v>6</v>
       </c>
       <c r="H84" t="n">
-        <v>10.2</v>
+        <v>6.8</v>
       </c>
       <c r="I84" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -15208,13 +15076,13 @@
         <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>12.92</v>
+        <v>13.34</v>
       </c>
       <c r="N84" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="O84" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr">
@@ -15224,24 +15092,24 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($155 to next deal) - confirm; Seasonal - last year ~10/wk vs 6 now, buy ahead?</t>
+          <t>Buy-month stock-up ($160 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Decoy Merlot 750ml</t>
+          <t>Line 39 Cabernet 750ml</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>669576019252</t>
+          <t>898756001057</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Merlot</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -15250,82 +15118,82 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="F85" t="n">
-        <v>24</v>
+        <v>26.2</v>
       </c>
       <c r="G85" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H85" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="I85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>12</v>
+        <v>132</v>
       </c>
       <c r="L85" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="M85" t="n">
-        <v>13.34</v>
+        <v>6.26</v>
       </c>
       <c r="N85" t="n">
-        <v>160</v>
+        <v>827</v>
       </c>
       <c r="O85" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr">
         <is>
-          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Sep, Oct) - stock up ~48wks to next deal</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($160 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($827 to next deal) - confirm; Seasonal - last year ~9/wk vs 6 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Line 39 Cabernet 750ml</t>
+          <t>Boen Tri Appellation Chardonnay 750ml</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>898756001057</t>
+          <t>856184006310</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>147</v>
+        <v>38</v>
       </c>
       <c r="F86" t="n">
-        <v>26.2</v>
+        <v>27.1</v>
       </c>
       <c r="G86" t="n">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="H86" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I86" t="n">
         <v>2</v>
@@ -15334,70 +15202,70 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>132</v>
+        <v>12</v>
       </c>
       <c r="L86" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>6.26</v>
+        <v>12.23</v>
       </c>
       <c r="N86" t="n">
-        <v>827</v>
+        <v>147</v>
       </c>
       <c r="O86" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr">
         <is>
-          <t>In buy-month (Sep, Oct) - stock up ~48wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($827 to next deal) - confirm; Seasonal - last year ~9/wk vs 6 now, buy ahead?</t>
+          <t>Buy-month stock-up ($147 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Boen Tri Appellation Chardonnay 750ml</t>
+          <t>Barefoot Merlot 750ml</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>856184006310</t>
+          <t>018341751109</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Merlot</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="F87" t="n">
-        <v>27.1</v>
+        <v>29.5</v>
       </c>
       <c r="G87" t="n">
-        <v>64</v>
+        <v>-27</v>
       </c>
       <c r="H87" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="I87" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K87" t="n">
         <v>12</v>
@@ -15406,40 +15274,40 @@
         <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>12.23</v>
+        <v>4.42</v>
       </c>
       <c r="N87" t="n">
-        <v>147</v>
+        <v>53</v>
       </c>
       <c r="O87" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($147 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($53 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Barefoot Merlot 750ml</t>
+          <t>Barefoot Pinot Noir 750ml</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>018341751109</t>
+          <t>085000017074</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Merlot</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -15448,22 +15316,22 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="F88" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="G88" t="n">
-        <v>-27</v>
+        <v>-22</v>
       </c>
       <c r="H88" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="I88" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J88" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
         <v>12</v>
@@ -15472,13 +15340,13 @@
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>4.42</v>
+        <v>4.32</v>
       </c>
       <c r="N88" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O88" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr">
@@ -15488,42 +15356,42 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($53 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($52 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Barefoot Pinot Noir 750ml</t>
+          <t>Banshee Paso Cab 750ml</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>085000017074</t>
+          <t>853868006345</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="F89" t="n">
-        <v>29.6</v>
+        <v>30.9</v>
       </c>
       <c r="G89" t="n">
-        <v>-22</v>
+        <v>45</v>
       </c>
       <c r="H89" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="I89" t="n">
         <v>2</v>
@@ -15538,10 +15406,10 @@
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>4.32</v>
+        <v>13.97</v>
       </c>
       <c r="N89" t="n">
-        <v>52</v>
+        <v>168</v>
       </c>
       <c r="O89" t="n">
         <v>46</v>
@@ -15549,50 +15417,50 @@
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, Mar, Jun, Aug, Oct, Nov) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($52 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($168 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Banshee Paso Cab 750ml</t>
+          <t>Bartenura Pinot Grigio 750ml</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>853868006345</t>
+          <t>087752003435</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Pinot Grigio/Gris</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>101</v>
+        <v>54</v>
       </c>
       <c r="F90" t="n">
-        <v>30.9</v>
+        <v>33.1</v>
       </c>
       <c r="G90" t="n">
-        <v>45</v>
+        <v>91</v>
       </c>
       <c r="H90" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="I90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -15604,61 +15472,61 @@
         <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>13.97</v>
+        <v>11.58</v>
       </c>
       <c r="N90" t="n">
-        <v>168</v>
+        <v>139</v>
       </c>
       <c r="O90" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Mar, Jun, Aug, Oct, Nov) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Feb, Apr, Jul, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($168 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($139 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>90+ Cellars 2019 Lot 26 Barolo 750ml</t>
+          <t>Barkan Cabernet Sauvignon 750ml</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>894655001440</t>
+          <t>087752006108</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Other Reds</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Bellboy Corporation</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="F91" t="n">
-        <v>33.1</v>
+        <v>41.8</v>
       </c>
       <c r="G91" t="n">
-        <v>-15</v>
+        <v>-43</v>
       </c>
       <c r="H91" t="n">
-        <v>4.2</v>
+        <v>0.2</v>
       </c>
       <c r="I91" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -15670,61 +15538,61 @@
         <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>17.44</v>
+        <v>9.75</v>
       </c>
       <c r="N91" t="n">
-        <v>209</v>
+        <v>117</v>
       </c>
       <c r="O91" t="n">
-        <v>56</v>
-      </c>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R91" t="inlineStr"/>
+        <v>39</v>
+      </c>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>In buy-month (Feb, Apr, Jul, Oct, Dec) - stock up ~9wks to next deal</t>
+        </is>
+      </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>Overstocked (33 wks on hand) - confirm before buying more; Seasonal - last year ~4/wk vs 3 now, buy ahead?</t>
+          <t>Buy-month stock-up ($117 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Bartenura Pinot Grigio 750ml</t>
+          <t>Apothic Inferno 750ml</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>087752003435</t>
+          <t>085000024904</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Pinot Grigio/Gris</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>54</v>
+        <v>186</v>
       </c>
       <c r="F92" t="n">
-        <v>33.1</v>
+        <v>44.3</v>
       </c>
       <c r="G92" t="n">
-        <v>91</v>
+        <v>-14</v>
       </c>
       <c r="H92" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I92" t="n">
         <v>2</v>
-      </c>
-      <c r="I92" t="n">
-        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -15736,40 +15604,40 @@
         <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>11.58</v>
+        <v>8.42</v>
       </c>
       <c r="N92" t="n">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="O92" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Apr, Jul, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($139 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($101 to next deal) - confirm; Seasonal - last year ~7/wk vs 4 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Barkan Cabernet Sauvignon 750ml</t>
+          <t>Rashi Claret 750ml</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>087752006108</t>
+          <t>087752008454</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15778,16 +15646,16 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="F93" t="n">
-        <v>41.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G93" t="n">
-        <v>-43</v>
+        <v>200</v>
       </c>
       <c r="H93" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="I93" t="n">
         <v>1</v>
@@ -15802,13 +15670,13 @@
         <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>9.75</v>
+        <v>7.62</v>
       </c>
       <c r="N93" t="n">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="O93" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr">
@@ -15817,138 +15685,6 @@
         </is>
       </c>
       <c r="S93" t="inlineStr">
-        <is>
-          <t>Buy-month stock-up ($117 to next deal) - confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Apothic Inferno 750ml</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>085000024904</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Red Blends</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Johnson Brothers - St. Paul</t>
-        </is>
-      </c>
-      <c r="E94" t="n">
-        <v>186</v>
-      </c>
-      <c r="F94" t="n">
-        <v>44.3</v>
-      </c>
-      <c r="G94" t="n">
-        <v>-14</v>
-      </c>
-      <c r="H94" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="I94" t="n">
-        <v>2</v>
-      </c>
-      <c r="J94" t="n">
-        <v>0</v>
-      </c>
-      <c r="K94" t="n">
-        <v>12</v>
-      </c>
-      <c r="L94" t="n">
-        <v>1</v>
-      </c>
-      <c r="M94" t="n">
-        <v>8.42</v>
-      </c>
-      <c r="N94" t="n">
-        <v>101</v>
-      </c>
-      <c r="O94" t="n">
-        <v>44</v>
-      </c>
-      <c r="Q94" t="inlineStr"/>
-      <c r="R94" t="inlineStr">
-        <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
-        </is>
-      </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>Buy-month stock-up ($101 to next deal) - confirm; Seasonal - last year ~7/wk vs 4 now, buy ahead?</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Rashi Claret 750ml</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>087752008454</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Red Blends</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
-        <v>82</v>
-      </c>
-      <c r="F95" t="n">
-        <v>87.90000000000001</v>
-      </c>
-      <c r="G95" t="n">
-        <v>200</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I95" t="n">
-        <v>1</v>
-      </c>
-      <c r="J95" t="n">
-        <v>0</v>
-      </c>
-      <c r="K95" t="n">
-        <v>12</v>
-      </c>
-      <c r="L95" t="n">
-        <v>1</v>
-      </c>
-      <c r="M95" t="n">
-        <v>7.62</v>
-      </c>
-      <c r="N95" t="n">
-        <v>91</v>
-      </c>
-      <c r="O95" t="n">
-        <v>34</v>
-      </c>
-      <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="inlineStr">
-        <is>
-          <t>In buy-month (Feb, Apr, Jul, Oct, Dec) - stock up ~9wks to next deal</t>
-        </is>
-      </c>
-      <c r="S95" t="inlineStr">
         <is>
           <t>Buy-month stock-up ($91 to next deal) - confirm</t>
         </is>

--- a/data/Wine Recommended Order.xlsx
+++ b/data/Wine Recommended Order.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S146"/>
+  <dimension ref="A1:S147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8714,38 +8714,38 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Boen Russian River Pinot Noir 750ml</t>
+          <t>Alexander Valley Vineyards Cab Franc 750ml</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>856184006211</t>
+          <t>085798049622</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F133" t="n">
         <v>25.7</v>
       </c>
       <c r="G133" t="n">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -8757,40 +8757,40 @@
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>21.33</v>
+        <v>17.33</v>
       </c>
       <c r="N133" t="n">
-        <v>256</v>
+        <v>208</v>
       </c>
       <c r="O133" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="Q133" t="inlineStr"/>
       <c r="R133" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Apr, Oct) - stock up ~26wks to next deal</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($256 to next deal) - confirm; Seasonal - last year ~2/wk vs 0 now, buy ahead?</t>
+          <t>Buy-month stock-up ($208 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Boen Tri Appellation Chardonnay 750ml</t>
+          <t>Boen Russian River Pinot Noir 750ml</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>856184006310</t>
+          <t>856184006211</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -8799,19 +8799,19 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="F134" t="n">
-        <v>26.4</v>
+        <v>25.7</v>
       </c>
       <c r="G134" t="n">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="H134" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="I134" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -8823,13 +8823,13 @@
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>12.22</v>
+        <v>21.33</v>
       </c>
       <c r="N134" t="n">
-        <v>147</v>
+        <v>256</v>
       </c>
       <c r="O134" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="Q134" t="inlineStr"/>
       <c r="R134" t="inlineStr">
@@ -8839,42 +8839,42 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($147 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($256 to next deal) - confirm; Seasonal - last year ~2/wk vs 0 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Daily's Blackberry Smash 10oz</t>
+          <t>Boen Tri Appellation Chardonnay 750ml</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>074806918975</t>
+          <t>856184006310</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>132</v>
+        <v>37</v>
       </c>
       <c r="F135" t="n">
-        <v>26.9</v>
+        <v>26.4</v>
       </c>
       <c r="G135" t="n">
-        <v>-34</v>
+        <v>50</v>
       </c>
       <c r="H135" t="n">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="I135" t="n">
         <v>3</v>
@@ -8883,46 +8883,46 @@
         <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="L135" t="n">
         <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>1.61</v>
+        <v>12.22</v>
       </c>
       <c r="N135" t="n">
-        <v>39</v>
+        <v>147</v>
       </c>
       <c r="O135" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="Q135" t="inlineStr"/>
       <c r="R135" t="inlineStr">
         <is>
-          <t>In buy-month (Sep, Oct, Nov, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($39 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($147 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Bartenura Pinot Grigio 750ml</t>
+          <t>Daily's Blackberry Smash 10oz</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>087752003435</t>
+          <t>074806918975</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Pinot Grigio/Gris</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -8931,16 +8931,16 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>53</v>
+        <v>132</v>
       </c>
       <c r="F136" t="n">
-        <v>28.4</v>
+        <v>26.9</v>
       </c>
       <c r="G136" t="n">
-        <v>100</v>
+        <v>-34</v>
       </c>
       <c r="H136" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="I136" t="n">
         <v>3</v>
@@ -8949,46 +8949,46 @@
         <v>0</v>
       </c>
       <c r="K136" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="L136" t="n">
         <v>1</v>
       </c>
       <c r="M136" t="n">
-        <v>11.57</v>
+        <v>1.61</v>
       </c>
       <c r="N136" t="n">
-        <v>139</v>
+        <v>39</v>
       </c>
       <c r="O136" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="Q136" t="inlineStr"/>
       <c r="R136" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Apr, Jul, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Sep, Oct, Nov, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($139 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($39 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Daily's Margarita RTD Frozen 10oz</t>
+          <t>Bartenura Pinot Grigio 750ml</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>074806184103</t>
+          <t>087752003435</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Pinot Grigio/Gris</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -8997,64 +8997,64 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>186</v>
+        <v>53</v>
       </c>
       <c r="F137" t="n">
-        <v>30.7</v>
+        <v>28.4</v>
       </c>
       <c r="G137" t="n">
-        <v>-48</v>
+        <v>100</v>
       </c>
       <c r="H137" t="n">
-        <v>5.8</v>
+        <v>2</v>
       </c>
       <c r="I137" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
       </c>
       <c r="K137" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="L137" t="n">
         <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>1.56</v>
+        <v>11.57</v>
       </c>
       <c r="N137" t="n">
-        <v>37</v>
+        <v>139</v>
       </c>
       <c r="O137" t="n">
-        <v>61</v>
+        <v>16</v>
       </c>
       <c r="Q137" t="inlineStr"/>
       <c r="R137" t="inlineStr">
         <is>
-          <t>In buy-month (Sep, Oct, Nov, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Feb, Apr, Jul, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($37 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($139 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Bartenura Moscato Rose 750ml</t>
+          <t>Daily's Margarita RTD Frozen 10oz</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>087752013854</t>
+          <t>074806184103</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Moscato</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -9063,82 +9063,82 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>15</v>
+        <v>186</v>
       </c>
       <c r="F138" t="n">
-        <v>32.1</v>
+        <v>30.7</v>
       </c>
       <c r="G138" t="n">
-        <v>50</v>
+        <v>-48</v>
       </c>
       <c r="H138" t="n">
-        <v>0.8</v>
+        <v>5.8</v>
       </c>
       <c r="I138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
       </c>
       <c r="K138" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="L138" t="n">
         <v>1</v>
       </c>
       <c r="M138" t="n">
-        <v>13.05</v>
+        <v>1.56</v>
       </c>
       <c r="N138" t="n">
-        <v>157</v>
+        <v>37</v>
       </c>
       <c r="O138" t="n">
-        <v>-4</v>
+        <v>61</v>
       </c>
       <c r="Q138" t="inlineStr"/>
       <c r="R138" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Apr, Jul, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Sep, Oct, Nov, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>Margin looks off - check retail/cost; Buy-month stock-up ($157 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($37 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Decoy Merlot 750ml</t>
+          <t>Bartenura Moscato Rose 750ml</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>669576019252</t>
+          <t>087752013854</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Merlot</t>
+          <t>Moscato</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="F139" t="n">
-        <v>32.9</v>
+        <v>32.1</v>
       </c>
       <c r="G139" t="n">
-        <v>-21</v>
+        <v>50</v>
       </c>
       <c r="H139" t="n">
-        <v>7.2</v>
+        <v>0.8</v>
       </c>
       <c r="I139" t="n">
         <v>1</v>
@@ -9153,40 +9153,40 @@
         <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>13.34</v>
+        <v>13.05</v>
       </c>
       <c r="N139" t="n">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="O139" t="n">
-        <v>39</v>
+        <v>-4</v>
       </c>
       <c r="Q139" t="inlineStr"/>
       <c r="R139" t="inlineStr">
         <is>
-          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Feb, Apr, Jul, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($160 to next deal) - confirm; Seasonal - last year ~7/wk vs 4 now, buy ahead?</t>
+          <t>Margin looks off - check retail/cost; Buy-month stock-up ($157 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Line 39 Cabernet 750ml</t>
+          <t>Decoy Merlot 750ml</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>898756001057</t>
+          <t>669576019252</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Merlot</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -9195,59 +9195,59 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="F140" t="n">
-        <v>34.8</v>
+        <v>32.9</v>
       </c>
       <c r="G140" t="n">
-        <v>-4</v>
+        <v>-21</v>
       </c>
       <c r="H140" t="n">
-        <v>9.5</v>
+        <v>7.2</v>
       </c>
       <c r="I140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
       </c>
       <c r="K140" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="L140" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M140" t="n">
-        <v>6.26</v>
+        <v>13.34</v>
       </c>
       <c r="N140" t="n">
-        <v>376</v>
+        <v>160</v>
       </c>
       <c r="O140" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="Q140" t="inlineStr"/>
       <c r="R140" t="inlineStr">
         <is>
-          <t>In buy-month (Sep, Oct) - stock up ~48wks to next deal</t>
+          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($376 to next deal) - confirm; Seasonal - last year ~10/wk vs 4 now, buy ahead?</t>
+          <t>Buy-month stock-up ($160 to next deal) - confirm; Seasonal - last year ~7/wk vs 4 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Banshee Paso Cab 750ml</t>
+          <t>Line 39 Cabernet 750ml</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>853868006345</t>
+          <t>898756001057</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9257,89 +9257,89 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>99</v>
+        <v>146</v>
       </c>
       <c r="F141" t="n">
-        <v>35.4</v>
+        <v>34.8</v>
       </c>
       <c r="G141" t="n">
-        <v>24</v>
+        <v>-4</v>
       </c>
       <c r="H141" t="n">
-        <v>4.2</v>
+        <v>9.5</v>
       </c>
       <c r="I141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
       </c>
       <c r="K141" t="n">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="L141" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M141" t="n">
-        <v>13.97</v>
+        <v>6.26</v>
       </c>
       <c r="N141" t="n">
-        <v>168</v>
+        <v>376</v>
       </c>
       <c r="O141" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Q141" t="inlineStr"/>
       <c r="R141" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Mar, Jun, Aug, Oct, Nov) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Sep, Oct) - stock up ~48wks to next deal</t>
         </is>
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($168 to next deal) - confirm; Seasonal - last year ~4/wk vs 3 now, buy ahead?</t>
+          <t>Buy-month stock-up ($376 to next deal) - confirm; Seasonal - last year ~10/wk vs 4 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Apothic Inferno 750ml</t>
+          <t>Banshee Paso Cab 750ml</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>085000024904</t>
+          <t>853868006345</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>183</v>
+        <v>99</v>
       </c>
       <c r="F142" t="n">
-        <v>37.3</v>
+        <v>35.4</v>
       </c>
       <c r="G142" t="n">
-        <v>-3</v>
+        <v>24</v>
       </c>
       <c r="H142" t="n">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="I142" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -9351,35 +9351,35 @@
         <v>1</v>
       </c>
       <c r="M142" t="n">
-        <v>8.4</v>
+        <v>13.97</v>
       </c>
       <c r="N142" t="n">
-        <v>101</v>
+        <v>168</v>
       </c>
       <c r="O142" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q142" t="inlineStr"/>
       <c r="R142" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, Mar, Jun, Aug, Oct, Nov) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($101 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($168 to next deal) - confirm; Seasonal - last year ~4/wk vs 3 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Ferrari Carano Siena 750ml</t>
+          <t>Apothic Inferno 750ml</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>742651184295</t>
+          <t>085000024904</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9389,23 +9389,23 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>137</v>
+        <v>183</v>
       </c>
       <c r="F143" t="n">
-        <v>39.1</v>
+        <v>37.3</v>
       </c>
       <c r="G143" t="n">
-        <v>12</v>
+        <v>-3</v>
       </c>
       <c r="H143" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="I143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -9417,61 +9417,61 @@
         <v>1</v>
       </c>
       <c r="M143" t="n">
-        <v>15.33</v>
+        <v>8.4</v>
       </c>
       <c r="N143" t="n">
-        <v>184</v>
+        <v>101</v>
       </c>
       <c r="O143" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q143" t="inlineStr"/>
       <c r="R143" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Mar, Jun, Aug, Oct, Nov) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($184 to next deal) - confirm; Seasonal - last year ~6/wk vs 4 now, buy ahead?</t>
+          <t>Buy-month stock-up ($101 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Decoy Zinfandel 750ml</t>
+          <t>Ferrari Carano Siena 750ml</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>669576019238</t>
+          <t>742651184295</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Zinfandel</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>47</v>
+        <v>137</v>
       </c>
       <c r="F144" t="n">
-        <v>40.3</v>
+        <v>39.1</v>
       </c>
       <c r="G144" t="n">
-        <v>-46</v>
+        <v>12</v>
       </c>
       <c r="H144" t="n">
-        <v>2.5</v>
+        <v>5.8</v>
       </c>
       <c r="I144" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -9483,40 +9483,40 @@
         <v>1</v>
       </c>
       <c r="M144" t="n">
-        <v>13.99</v>
+        <v>15.33</v>
       </c>
       <c r="N144" t="n">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="O144" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="Q144" t="inlineStr"/>
       <c r="R144" t="inlineStr">
         <is>
-          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Feb, Mar, Jun, Aug, Oct, Nov) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($168 to next deal) - confirm; Seasonal - last year ~2/wk vs 1 now, buy ahead?</t>
+          <t>Buy-month stock-up ($184 to next deal) - confirm; Seasonal - last year ~6/wk vs 4 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Line 39 Sauvignon Blanc 750ml</t>
+          <t>Decoy Zinfandel 750ml</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>898756001040</t>
+          <t>669576019238</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Sauvignon Blanc</t>
+          <t>Zinfandel</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -9525,19 +9525,19 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>140</v>
+        <v>47</v>
       </c>
       <c r="F145" t="n">
-        <v>60</v>
+        <v>40.3</v>
       </c>
       <c r="G145" t="n">
-        <v>-25</v>
+        <v>-46</v>
       </c>
       <c r="H145" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="I145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -9549,61 +9549,61 @@
         <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>6.29</v>
+        <v>13.99</v>
       </c>
       <c r="N145" t="n">
-        <v>75</v>
+        <v>168</v>
       </c>
       <c r="O145" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="Q145" t="inlineStr"/>
       <c r="R145" t="inlineStr">
         <is>
-          <t>In buy-month (Sep, Oct) - stock up ~48wks to next deal</t>
+          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($75 to next deal) - confirm; Seasonal - last year ~5/wk vs 2 now, buy ahead?</t>
+          <t>Buy-month stock-up ($168 to next deal) - confirm; Seasonal - last year ~2/wk vs 1 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Rashi Claret 750ml</t>
+          <t>Line 39 Sauvignon Blanc 750ml</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>087752008454</t>
+          <t>898756001040</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Sauvignon Blanc</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="F146" t="n">
-        <v>87.90000000000001</v>
+        <v>60</v>
       </c>
       <c r="G146" t="n">
-        <v>200</v>
+        <v>-25</v>
       </c>
       <c r="H146" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="I146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -9615,21 +9615,87 @@
         <v>1</v>
       </c>
       <c r="M146" t="n">
-        <v>7.62</v>
+        <v>6.29</v>
       </c>
       <c r="N146" t="n">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="O146" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="Q146" t="inlineStr"/>
       <c r="R146" t="inlineStr">
         <is>
+          <t>In buy-month (Sep, Oct) - stock up ~48wks to next deal</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>Buy-month stock-up ($75 to next deal) - confirm; Seasonal - last year ~5/wk vs 2 now, buy ahead?</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Rashi Claret 750ml</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>087752008454</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Red Blends</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>82</v>
+      </c>
+      <c r="F147" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="G147" t="n">
+        <v>200</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I147" t="n">
+        <v>1</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" t="n">
+        <v>12</v>
+      </c>
+      <c r="L147" t="n">
+        <v>1</v>
+      </c>
+      <c r="M147" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="N147" t="n">
+        <v>91</v>
+      </c>
+      <c r="O147" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q147" t="inlineStr"/>
+      <c r="R147" t="inlineStr">
+        <is>
           <t>In buy-month (Feb, Apr, Jul, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
-      <c r="S146" t="inlineStr">
+      <c r="S147" t="inlineStr">
         <is>
           <t>Buy-month stock-up ($91 to next deal) - confirm</t>
         </is>
@@ -9646,7 +9712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S96"/>
+  <dimension ref="A1:S97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15083,38 +15149,38 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Boen Russian River Pinot Noir 750ml</t>
+          <t>Alexander Valley Vineyards Cab Franc 750ml</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>856184006211</t>
+          <t>085798049622</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F83" t="n">
         <v>25.7</v>
       </c>
       <c r="G83" t="n">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -15126,40 +15192,40 @@
         <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>21.33</v>
+        <v>17.33</v>
       </c>
       <c r="N83" t="n">
-        <v>256</v>
+        <v>208</v>
       </c>
       <c r="O83" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Apr, Oct) - stock up ~26wks to next deal</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($256 to next deal) - confirm; Seasonal - last year ~2/wk vs 0 now, buy ahead?</t>
+          <t>Buy-month stock-up ($208 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Boen Tri Appellation Chardonnay 750ml</t>
+          <t>Boen Russian River Pinot Noir 750ml</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>856184006310</t>
+          <t>856184006211</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -15168,19 +15234,19 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="F84" t="n">
-        <v>26.4</v>
+        <v>25.7</v>
       </c>
       <c r="G84" t="n">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="H84" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="I84" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -15192,13 +15258,13 @@
         <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>12.22</v>
+        <v>21.33</v>
       </c>
       <c r="N84" t="n">
-        <v>147</v>
+        <v>256</v>
       </c>
       <c r="O84" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr">
@@ -15208,42 +15274,42 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($147 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($256 to next deal) - confirm; Seasonal - last year ~2/wk vs 0 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Daily's Blackberry Smash 10oz</t>
+          <t>Boen Tri Appellation Chardonnay 750ml</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>074806918975</t>
+          <t>856184006310</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>132</v>
+        <v>37</v>
       </c>
       <c r="F85" t="n">
-        <v>26.9</v>
+        <v>26.4</v>
       </c>
       <c r="G85" t="n">
-        <v>-34</v>
+        <v>50</v>
       </c>
       <c r="H85" t="n">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="I85" t="n">
         <v>3</v>
@@ -15252,46 +15318,46 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="L85" t="n">
         <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>1.61</v>
+        <v>12.22</v>
       </c>
       <c r="N85" t="n">
-        <v>39</v>
+        <v>147</v>
       </c>
       <c r="O85" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr">
         <is>
-          <t>In buy-month (Sep, Oct, Nov, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($39 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($147 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Bartenura Pinot Grigio 750ml</t>
+          <t>Daily's Blackberry Smash 10oz</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>087752003435</t>
+          <t>074806918975</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Pinot Grigio/Gris</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -15300,16 +15366,16 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>53</v>
+        <v>132</v>
       </c>
       <c r="F86" t="n">
-        <v>28.4</v>
+        <v>26.9</v>
       </c>
       <c r="G86" t="n">
-        <v>100</v>
+        <v>-34</v>
       </c>
       <c r="H86" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="I86" t="n">
         <v>3</v>
@@ -15318,46 +15384,46 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="L86" t="n">
         <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>11.57</v>
+        <v>1.61</v>
       </c>
       <c r="N86" t="n">
-        <v>139</v>
+        <v>39</v>
       </c>
       <c r="O86" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Apr, Jul, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Sep, Oct, Nov, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($139 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($39 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Daily's Margarita RTD Frozen 10oz</t>
+          <t>Bartenura Pinot Grigio 750ml</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>074806184103</t>
+          <t>087752003435</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Pinot Grigio/Gris</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -15366,64 +15432,64 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>186</v>
+        <v>53</v>
       </c>
       <c r="F87" t="n">
-        <v>30.7</v>
+        <v>28.4</v>
       </c>
       <c r="G87" t="n">
-        <v>-48</v>
+        <v>100</v>
       </c>
       <c r="H87" t="n">
-        <v>5.8</v>
+        <v>2</v>
       </c>
       <c r="I87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="L87" t="n">
         <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>1.56</v>
+        <v>11.57</v>
       </c>
       <c r="N87" t="n">
-        <v>37</v>
+        <v>139</v>
       </c>
       <c r="O87" t="n">
-        <v>61</v>
+        <v>16</v>
       </c>
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr">
         <is>
-          <t>In buy-month (Sep, Oct, Nov, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Feb, Apr, Jul, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($37 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($139 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Bartenura Moscato Rose 750ml</t>
+          <t>Daily's Margarita RTD Frozen 10oz</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>087752013854</t>
+          <t>074806184103</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Moscato</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -15432,82 +15498,82 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>15</v>
+        <v>186</v>
       </c>
       <c r="F88" t="n">
-        <v>32.1</v>
+        <v>30.7</v>
       </c>
       <c r="G88" t="n">
-        <v>50</v>
+        <v>-48</v>
       </c>
       <c r="H88" t="n">
-        <v>0.8</v>
+        <v>5.8</v>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="L88" t="n">
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>13.05</v>
+        <v>1.56</v>
       </c>
       <c r="N88" t="n">
-        <v>157</v>
+        <v>37</v>
       </c>
       <c r="O88" t="n">
-        <v>-4</v>
+        <v>61</v>
       </c>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Apr, Jul, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Sep, Oct, Nov, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>Margin looks off - check retail/cost; Buy-month stock-up ($157 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($37 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Decoy Merlot 750ml</t>
+          <t>Bartenura Moscato Rose 750ml</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>669576019252</t>
+          <t>087752013854</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Merlot</t>
+          <t>Moscato</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="F89" t="n">
-        <v>32.9</v>
+        <v>32.1</v>
       </c>
       <c r="G89" t="n">
-        <v>-21</v>
+        <v>50</v>
       </c>
       <c r="H89" t="n">
-        <v>7.2</v>
+        <v>0.8</v>
       </c>
       <c r="I89" t="n">
         <v>1</v>
@@ -15522,40 +15588,40 @@
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>13.34</v>
+        <v>13.05</v>
       </c>
       <c r="N89" t="n">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="O89" t="n">
-        <v>39</v>
+        <v>-4</v>
       </c>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr">
         <is>
-          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Feb, Apr, Jul, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($160 to next deal) - confirm; Seasonal - last year ~7/wk vs 4 now, buy ahead?</t>
+          <t>Margin looks off - check retail/cost; Buy-month stock-up ($157 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Line 39 Cabernet 750ml</t>
+          <t>Decoy Merlot 750ml</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>898756001057</t>
+          <t>669576019252</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Merlot</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -15564,59 +15630,59 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="F90" t="n">
-        <v>34.8</v>
+        <v>32.9</v>
       </c>
       <c r="G90" t="n">
-        <v>-4</v>
+        <v>-21</v>
       </c>
       <c r="H90" t="n">
-        <v>9.5</v>
+        <v>7.2</v>
       </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="L90" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>6.26</v>
+        <v>13.34</v>
       </c>
       <c r="N90" t="n">
-        <v>376</v>
+        <v>160</v>
       </c>
       <c r="O90" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr">
         <is>
-          <t>In buy-month (Sep, Oct) - stock up ~48wks to next deal</t>
+          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($376 to next deal) - confirm; Seasonal - last year ~10/wk vs 4 now, buy ahead?</t>
+          <t>Buy-month stock-up ($160 to next deal) - confirm; Seasonal - last year ~7/wk vs 4 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Banshee Paso Cab 750ml</t>
+          <t>Line 39 Cabernet 750ml</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>853868006345</t>
+          <t>898756001057</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -15626,89 +15692,89 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>99</v>
+        <v>146</v>
       </c>
       <c r="F91" t="n">
-        <v>35.4</v>
+        <v>34.8</v>
       </c>
       <c r="G91" t="n">
-        <v>24</v>
+        <v>-4</v>
       </c>
       <c r="H91" t="n">
-        <v>4.2</v>
+        <v>9.5</v>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="L91" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M91" t="n">
-        <v>13.97</v>
+        <v>6.26</v>
       </c>
       <c r="N91" t="n">
-        <v>168</v>
+        <v>376</v>
       </c>
       <c r="O91" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Mar, Jun, Aug, Oct, Nov) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Sep, Oct) - stock up ~48wks to next deal</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($168 to next deal) - confirm; Seasonal - last year ~4/wk vs 3 now, buy ahead?</t>
+          <t>Buy-month stock-up ($376 to next deal) - confirm; Seasonal - last year ~10/wk vs 4 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Apothic Inferno 750ml</t>
+          <t>Banshee Paso Cab 750ml</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>085000024904</t>
+          <t>853868006345</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>183</v>
+        <v>99</v>
       </c>
       <c r="F92" t="n">
-        <v>37.3</v>
+        <v>35.4</v>
       </c>
       <c r="G92" t="n">
-        <v>-3</v>
+        <v>24</v>
       </c>
       <c r="H92" t="n">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="I92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -15720,35 +15786,35 @@
         <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>8.4</v>
+        <v>13.97</v>
       </c>
       <c r="N92" t="n">
-        <v>101</v>
+        <v>168</v>
       </c>
       <c r="O92" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, Mar, Jun, Aug, Oct, Nov) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($101 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($168 to next deal) - confirm; Seasonal - last year ~4/wk vs 3 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Ferrari Carano Siena 750ml</t>
+          <t>Apothic Inferno 750ml</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>742651184295</t>
+          <t>085000024904</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -15758,23 +15824,23 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>137</v>
+        <v>183</v>
       </c>
       <c r="F93" t="n">
-        <v>39.1</v>
+        <v>37.3</v>
       </c>
       <c r="G93" t="n">
-        <v>12</v>
+        <v>-3</v>
       </c>
       <c r="H93" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="I93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -15786,61 +15852,61 @@
         <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>15.33</v>
+        <v>8.4</v>
       </c>
       <c r="N93" t="n">
-        <v>184</v>
+        <v>101</v>
       </c>
       <c r="O93" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Mar, Jun, Aug, Oct, Nov) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($184 to next deal) - confirm; Seasonal - last year ~6/wk vs 4 now, buy ahead?</t>
+          <t>Buy-month stock-up ($101 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Decoy Zinfandel 750ml</t>
+          <t>Ferrari Carano Siena 750ml</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>669576019238</t>
+          <t>742651184295</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Zinfandel</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>47</v>
+        <v>137</v>
       </c>
       <c r="F94" t="n">
-        <v>40.3</v>
+        <v>39.1</v>
       </c>
       <c r="G94" t="n">
-        <v>-46</v>
+        <v>12</v>
       </c>
       <c r="H94" t="n">
-        <v>2.5</v>
+        <v>5.8</v>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -15852,40 +15918,40 @@
         <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>13.99</v>
+        <v>15.33</v>
       </c>
       <c r="N94" t="n">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="O94" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr">
         <is>
-          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Feb, Mar, Jun, Aug, Oct, Nov) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($168 to next deal) - confirm; Seasonal - last year ~2/wk vs 1 now, buy ahead?</t>
+          <t>Buy-month stock-up ($184 to next deal) - confirm; Seasonal - last year ~6/wk vs 4 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Line 39 Sauvignon Blanc 750ml</t>
+          <t>Decoy Zinfandel 750ml</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>898756001040</t>
+          <t>669576019238</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sauvignon Blanc</t>
+          <t>Zinfandel</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15894,19 +15960,19 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>140</v>
+        <v>47</v>
       </c>
       <c r="F95" t="n">
-        <v>60</v>
+        <v>40.3</v>
       </c>
       <c r="G95" t="n">
-        <v>-25</v>
+        <v>-46</v>
       </c>
       <c r="H95" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="I95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -15918,61 +15984,61 @@
         <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>6.29</v>
+        <v>13.99</v>
       </c>
       <c r="N95" t="n">
-        <v>75</v>
+        <v>168</v>
       </c>
       <c r="O95" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr">
         <is>
-          <t>In buy-month (Sep, Oct) - stock up ~48wks to next deal</t>
+          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($75 to next deal) - confirm; Seasonal - last year ~5/wk vs 2 now, buy ahead?</t>
+          <t>Buy-month stock-up ($168 to next deal) - confirm; Seasonal - last year ~2/wk vs 1 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Rashi Claret 750ml</t>
+          <t>Line 39 Sauvignon Blanc 750ml</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>087752008454</t>
+          <t>898756001040</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Sauvignon Blanc</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="F96" t="n">
-        <v>87.90000000000001</v>
+        <v>60</v>
       </c>
       <c r="G96" t="n">
-        <v>200</v>
+        <v>-25</v>
       </c>
       <c r="H96" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -15984,21 +16050,87 @@
         <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>7.62</v>
+        <v>6.29</v>
       </c>
       <c r="N96" t="n">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="O96" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr">
         <is>
+          <t>In buy-month (Sep, Oct) - stock up ~48wks to next deal</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>Buy-month stock-up ($75 to next deal) - confirm; Seasonal - last year ~5/wk vs 2 now, buy ahead?</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Rashi Claret 750ml</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>087752008454</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Red Blends</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>82</v>
+      </c>
+      <c r="F97" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="G97" t="n">
+        <v>200</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I97" t="n">
+        <v>1</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
+        <v>12</v>
+      </c>
+      <c r="L97" t="n">
+        <v>1</v>
+      </c>
+      <c r="M97" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="N97" t="n">
+        <v>91</v>
+      </c>
+      <c r="O97" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr">
+        <is>
           <t>In buy-month (Feb, Apr, Jul, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
-      <c r="S96" t="inlineStr">
+      <c r="S97" t="inlineStr">
         <is>
           <t>Buy-month stock-up ($91 to next deal) - confirm</t>
         </is>
@@ -16015,7 +16147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q29"/>
+  <dimension ref="A1:Q31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16108,17 +16240,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cavit Pinot Grigio 1.5L</t>
+          <t>Alexander Valley Vineyards Cab Sauv 750ml</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>086785000039</t>
+          <t>085798028726</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pinot Grigio/Gris</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -16127,54 +16259,54 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>273</v>
+        <v>38</v>
       </c>
       <c r="F2" t="n">
-        <v>12.1</v>
+        <v>7.8</v>
       </c>
       <c r="G2" t="n">
+        <v>29</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
         <v>4</v>
       </c>
-      <c r="H2" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="I2" t="n">
-        <v>25</v>
-      </c>
       <c r="J2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>12</v>
+        <v>96</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M2" t="n">
-        <v>8.83</v>
+        <v>15.02</v>
       </c>
       <c r="N2" t="n">
-        <v>106</v>
+        <v>1442</v>
       </c>
       <c r="O2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cavit Pinot Grigio 750ml</t>
+          <t>Alexander Valley Vineyards Chardonnay 750ml</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>086785000084</t>
+          <t>085798018727</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pinot Grigio/Gris</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -16183,146 +16315,146 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="F3" t="n">
-        <v>4.1</v>
+        <v>16.5</v>
       </c>
       <c r="G3" t="n">
-        <v>43</v>
+        <v>-5</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M3" t="n">
-        <v>6.67</v>
+        <v>11.26</v>
       </c>
       <c r="N3" t="n">
-        <v>160</v>
+        <v>405</v>
       </c>
       <c r="O3" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Franzia Cab Sauv 5L Box</t>
+          <t>Cavit Pinot Grigio 1.5L</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>083120101895</t>
+          <t>086785000039</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Pinot Grigio/Gris</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>52</v>
+        <v>273</v>
       </c>
       <c r="F4" t="n">
-        <v>3.8</v>
+        <v>12.1</v>
       </c>
       <c r="G4" t="n">
         <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>13.2</v>
+        <v>26.8</v>
       </c>
       <c r="I4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="K4" t="n">
         <v>12</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
-        <v>14</v>
+        <v>8.83</v>
       </c>
       <c r="N4" t="n">
-        <v>168</v>
+        <v>106</v>
       </c>
       <c r="O4" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Franzia Chablis 5L Box</t>
+          <t>Cavit Pinot Grigio 750ml</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>083120102793</t>
+          <t>086785000084</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>White Blends</t>
+          <t>Pinot Grigio/Gris</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4</v>
+        <v>4.1</v>
       </c>
       <c r="G5" t="n">
-        <v>94</v>
+        <v>43</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="L5" t="n">
         <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>14</v>
+        <v>6.67</v>
       </c>
       <c r="N5" t="n">
-        <v>112</v>
+        <v>160</v>
       </c>
       <c r="O5" t="n">
         <v>33</v>
@@ -16332,17 +16464,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Franzia Chardonnay 5L Box</t>
+          <t>Franzia Cab Sauv 5L Box</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>083120102090</t>
+          <t>083120101895</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -16351,49 +16483,49 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>30.5</v>
+        <v>13.2</v>
       </c>
       <c r="I6" t="n">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K6" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="L6" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
         <v>14</v>
       </c>
       <c r="N6" t="n">
-        <v>840</v>
+        <v>168</v>
       </c>
       <c r="O6" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Franzia Crisp White 5L Box</t>
+          <t>Franzia Chablis 5L Box</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>083120102892</t>
+          <t>083120102793</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -16407,54 +16539,54 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="G7" t="n">
-        <v>31</v>
+        <v>94</v>
       </c>
       <c r="H7" t="n">
-        <v>25.5</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>113</v>
+        <v>9</v>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>108</v>
+        <v>8</v>
       </c>
       <c r="L7" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>11.82</v>
+        <v>14</v>
       </c>
       <c r="N7" t="n">
-        <v>1276</v>
+        <v>112</v>
       </c>
       <c r="O7" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Franzia Fruity Red Sangria 5L Box</t>
+          <t>Franzia Chardonnay 5L Box</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>083120103295</t>
+          <t>083120102090</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -16463,54 +16595,54 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>30</v>
+        <v>87</v>
       </c>
       <c r="F8" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="G8" t="n">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>4.8</v>
+        <v>30.5</v>
       </c>
       <c r="I8" t="n">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="J8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="M8" t="n">
-        <v>11.82</v>
+        <v>14</v>
       </c>
       <c r="N8" t="n">
-        <v>142</v>
+        <v>840</v>
       </c>
       <c r="O8" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Franzia Moscato 5L Box</t>
+          <t>Franzia Crisp White 5L Box</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>083120003021</t>
+          <t>083120102892</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Other Whites</t>
+          <t>White Blends</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -16519,54 +16651,54 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F9" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="G9" t="n">
+        <v>31</v>
+      </c>
+      <c r="H9" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>113</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" t="n">
+        <v>108</v>
+      </c>
+      <c r="L9" t="n">
+        <v>27</v>
+      </c>
+      <c r="M9" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1276</v>
+      </c>
+      <c r="O9" t="n">
         <v>34</v>
-      </c>
-      <c r="H9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="I9" t="n">
-        <v>41</v>
-      </c>
-      <c r="J9" t="n">
-        <v>8</v>
-      </c>
-      <c r="K9" t="n">
-        <v>32</v>
-      </c>
-      <c r="L9" t="n">
-        <v>8</v>
-      </c>
-      <c r="M9" t="n">
-        <v>14</v>
-      </c>
-      <c r="N9" t="n">
-        <v>448</v>
-      </c>
-      <c r="O9" t="n">
-        <v>22</v>
       </c>
       <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Franzia Pink Moscato 5L Box</t>
+          <t>Franzia Fruity Red Sangria 5L Box</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>083120003540</t>
+          <t>083120103295</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Other Whites</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -16575,54 +16707,54 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="G10" t="n">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="H10" t="n">
-        <v>19.2</v>
+        <v>4.8</v>
       </c>
       <c r="I10" t="n">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="J10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K10" t="n">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="L10" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="M10" t="n">
-        <v>14</v>
+        <v>11.82</v>
       </c>
       <c r="N10" t="n">
-        <v>1120</v>
+        <v>142</v>
       </c>
       <c r="O10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Franzia Pinot Grigio 5L Box</t>
+          <t>Franzia Moscato 5L Box</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>083120100393</t>
+          <t>083120003021</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pinot Grigio/Gris</t>
+          <t>Other Whites</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -16631,54 +16763,54 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="G11" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="H11" t="n">
-        <v>23.8</v>
+        <v>16.5</v>
       </c>
       <c r="I11" t="n">
-        <v>92</v>
+        <v>41</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K11" t="n">
-        <v>92</v>
+        <v>32</v>
       </c>
       <c r="L11" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="M11" t="n">
         <v>14</v>
       </c>
       <c r="N11" t="n">
-        <v>1288</v>
+        <v>448</v>
       </c>
       <c r="O11" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Franzia Pinot Noir 5L Box</t>
+          <t>Franzia Pink Moscato 5L Box</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>083120003823</t>
+          <t>083120003540</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Other Whites</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -16687,54 +16819,54 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="F12" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="G12" t="n">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="I12" t="n">
-        <v>8</v>
+        <v>84</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K12" t="n">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="M12" t="n">
         <v>14</v>
       </c>
       <c r="N12" t="n">
-        <v>112</v>
+        <v>1120</v>
       </c>
       <c r="O12" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Franzia Refreshing White 5L Box</t>
+          <t>Franzia Pinot Grigio 5L Box</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>083120101994</t>
+          <t>083120100393</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>White Blends</t>
+          <t>Pinot Grigio/Gris</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -16743,54 +16875,54 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="F13" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="G13" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="H13" t="n">
-        <v>12.5</v>
+        <v>23.8</v>
       </c>
       <c r="I13" t="n">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>36</v>
+        <v>92</v>
       </c>
       <c r="L13" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="M13" t="n">
-        <v>11.82</v>
+        <v>14</v>
       </c>
       <c r="N13" t="n">
-        <v>425</v>
+        <v>1288</v>
       </c>
       <c r="O13" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Franzia Rich and Buttery Chardonnay 5L Box</t>
+          <t>Franzia Pinot Noir 5L Box</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>083120010128</t>
+          <t>083120003823</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -16799,19 +16931,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F14" t="n">
         <v>3.6</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="H14" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -16823,30 +16955,30 @@
         <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>41.76</v>
+        <v>14</v>
       </c>
       <c r="N14" t="n">
-        <v>334</v>
+        <v>112</v>
       </c>
       <c r="O14" t="n">
-        <v>-99</v>
+        <v>44</v>
       </c>
       <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Franzia Sauvignon Blanc 5L Box</t>
+          <t>Franzia Refreshing White 5L Box</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>083120011231</t>
+          <t>083120101994</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sauvignon Blanc</t>
+          <t>White Blends</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -16855,54 +16987,54 @@
         </is>
       </c>
       <c r="E15" t="n">
+        <v>45</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>37</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I15" t="n">
+        <v>35</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>36</v>
+      </c>
+      <c r="L15" t="n">
         <v>9</v>
       </c>
-      <c r="F15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G15" t="n">
-        <v>11</v>
-      </c>
-      <c r="H15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I15" t="n">
-        <v>11</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>12</v>
-      </c>
-      <c r="L15" t="n">
-        <v>3</v>
-      </c>
       <c r="M15" t="n">
-        <v>14</v>
+        <v>11.82</v>
       </c>
       <c r="N15" t="n">
-        <v>168</v>
+        <v>425</v>
       </c>
       <c r="O15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Franzia Sunset Blush 5L Box</t>
+          <t>Franzia Rich and Buttery Chardonnay 5L Box</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>083120103691</t>
+          <t>083120010128</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -16911,54 +17043,54 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>81</v>
+        <v>16</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="G16" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>17.2</v>
+        <v>4.8</v>
       </c>
       <c r="I16" t="n">
-        <v>77</v>
+        <v>7</v>
       </c>
       <c r="J16" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="L16" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>10.04</v>
+        <v>41.76</v>
       </c>
       <c r="N16" t="n">
-        <v>602</v>
+        <v>334</v>
       </c>
       <c r="O16" t="n">
-        <v>44</v>
+        <v>-99</v>
       </c>
       <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Franzia White Zinfandel 5L Box</t>
+          <t>Franzia Sauvignon Blanc 5L Box</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>083120103196</t>
+          <t>083120011231</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Zinfandel</t>
+          <t>Sauvignon Blanc</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -16967,34 +17099,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="G17" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="H17" t="n">
-        <v>20</v>
+        <v>3.5</v>
       </c>
       <c r="I17" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="J17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="L17" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="M17" t="n">
         <v>14</v>
       </c>
       <c r="N17" t="n">
-        <v>672</v>
+        <v>168</v>
       </c>
       <c r="O17" t="n">
         <v>33</v>
@@ -17004,129 +17136,129 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Louis Jadot Beaujolais Village 750ml</t>
+          <t>Franzia Sunset Blush 5L Box</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>084692400546</t>
+          <t>083120103691</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Other Reds</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>175</v>
+        <v>81</v>
       </c>
       <c r="F18" t="n">
-        <v>21.4</v>
+        <v>2.4</v>
       </c>
       <c r="G18" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="H18" t="n">
-        <v>13.2</v>
+        <v>17.2</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K18" t="n">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="M18" t="n">
-        <v>9.76</v>
+        <v>10.04</v>
       </c>
       <c r="N18" t="n">
-        <v>117</v>
+        <v>602</v>
       </c>
       <c r="O18" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Louis Jadot Macon Village 750ml</t>
+          <t>Franzia White Zinfandel 5L Box</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>084692418541</t>
+          <t>083120103196</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Zinfandel</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F19" t="n">
-        <v>14.8</v>
+        <v>2.4</v>
       </c>
       <c r="G19" t="n">
+        <v>30</v>
+      </c>
+      <c r="H19" t="n">
+        <v>20</v>
+      </c>
+      <c r="I19" t="n">
+        <v>50</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>48</v>
+      </c>
+      <c r="L19" t="n">
         <v>12</v>
       </c>
-      <c r="H19" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>12</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
       <c r="M19" t="n">
-        <v>11.73</v>
+        <v>14</v>
       </c>
       <c r="N19" t="n">
-        <v>141</v>
+        <v>672</v>
       </c>
       <c r="O19" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>St. Francis Cab 750ml</t>
+          <t>Louis Jadot Beaujolais Village 750ml</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>088534001380</t>
+          <t>084692400546</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Other Reds</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -17135,19 +17267,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5</v>
+        <v>175</v>
       </c>
       <c r="F20" t="n">
-        <v>7.1</v>
+        <v>21.4</v>
       </c>
       <c r="G20" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>13.2</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -17159,30 +17291,30 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>6.41</v>
+        <v>9.76</v>
       </c>
       <c r="N20" t="n">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="O20" t="n">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Stella Rosa Berry 750ml</t>
+          <t>Louis Jadot Macon Village 750ml</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>087872632225</t>
+          <t>084692418541</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -17191,54 +17323,54 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>118</v>
+        <v>62</v>
       </c>
       <c r="F21" t="n">
-        <v>13</v>
+        <v>14.8</v>
       </c>
       <c r="G21" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H21" t="n">
-        <v>10.5</v>
+        <v>6.2</v>
       </c>
       <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
         <v>12</v>
       </c>
-      <c r="J21" t="n">
-        <v>12</v>
-      </c>
-      <c r="K21" t="n">
-        <v>84</v>
-      </c>
       <c r="L21" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>8.470000000000001</v>
+        <v>11.73</v>
       </c>
       <c r="N21" t="n">
-        <v>712</v>
+        <v>141</v>
       </c>
       <c r="O21" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Stella Rosa Black 750ml</t>
+          <t>St. Francis Cab 750ml</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>087872633369</t>
+          <t>088534001380</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -17247,49 +17379,49 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>95</v>
+        <v>5</v>
       </c>
       <c r="F22" t="n">
-        <v>3.9</v>
+        <v>7.1</v>
       </c>
       <c r="G22" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="H22" t="n">
-        <v>17.2</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>444</v>
+        <v>12</v>
       </c>
       <c r="L22" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>8.6</v>
+        <v>6.41</v>
       </c>
       <c r="N22" t="n">
-        <v>3817</v>
+        <v>77</v>
       </c>
       <c r="O22" t="n">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Stella Rosa Blueberry 750ml</t>
+          <t>Stella Rosa Berry 750ml</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>087872630931</t>
+          <t>087872632225</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -17303,34 +17435,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="F23" t="n">
-        <v>9.300000000000001</v>
+        <v>13</v>
       </c>
       <c r="G23" t="n">
-        <v>-6</v>
+        <v>7</v>
       </c>
       <c r="H23" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="I23" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J23" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="K23" t="n">
-        <v>144</v>
+        <v>84</v>
       </c>
       <c r="L23" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M23" t="n">
-        <v>8.6</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>1238</v>
+        <v>712</v>
       </c>
       <c r="O23" t="n">
         <v>39</v>
@@ -17340,17 +17472,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Stella Rosa Moscato D'Asti 750ml</t>
+          <t>Stella Rosa Black 750ml</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>087872630122</t>
+          <t>087872633369</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sparkling</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -17359,49 +17491,49 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="F24" t="n">
-        <v>10.3</v>
+        <v>3.9</v>
       </c>
       <c r="G24" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H24" t="n">
-        <v>8.5</v>
+        <v>17.2</v>
       </c>
       <c r="I24" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="J24" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="K24" t="n">
-        <v>132</v>
+        <v>444</v>
       </c>
       <c r="L24" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="M24" t="n">
-        <v>8.41</v>
+        <v>8.6</v>
       </c>
       <c r="N24" t="n">
-        <v>1111</v>
+        <v>3817</v>
       </c>
       <c r="O24" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Stella Rosa Peach 750ml</t>
+          <t>Stella Rosa Blueberry 750ml</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>087872632218</t>
+          <t>087872630931</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -17415,34 +17547,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="F25" t="n">
-        <v>14.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>4</v>
+        <v>-6</v>
       </c>
       <c r="H25" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="K25" t="n">
-        <v>60</v>
+        <v>144</v>
       </c>
       <c r="L25" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="M25" t="n">
-        <v>8.58</v>
+        <v>8.6</v>
       </c>
       <c r="N25" t="n">
-        <v>515</v>
+        <v>1238</v>
       </c>
       <c r="O25" t="n">
         <v>39</v>
@@ -17452,17 +17584,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Stella Rosa Pineapple 750ml</t>
+          <t>Stella Rosa Moscato D'Asti 750ml</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>087872638401</t>
+          <t>087872630122</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Sparkling</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -17471,49 +17603,49 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>111</v>
       </c>
       <c r="F26" t="n">
-        <v>7.1</v>
+        <v>10.3</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8</v>
+        <v>8.5</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K26" t="n">
-        <v>12</v>
+        <v>132</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="M26" t="n">
-        <v>8</v>
+        <v>8.41</v>
       </c>
       <c r="N26" t="n">
-        <v>96</v>
+        <v>1111</v>
       </c>
       <c r="O26" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Stella Rosa Red 750ml</t>
+          <t>Stella Rosa Peach 750ml</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>087872633406</t>
+          <t>087872632218</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -17527,49 +17659,49 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="F27" t="n">
-        <v>10.1</v>
+        <v>14.5</v>
       </c>
       <c r="G27" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H27" t="n">
-        <v>11.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J27" t="n">
         <v>4</v>
       </c>
       <c r="K27" t="n">
-        <v>168</v>
+        <v>60</v>
       </c>
       <c r="L27" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="M27" t="n">
-        <v>9.4</v>
+        <v>8.58</v>
       </c>
       <c r="N27" t="n">
-        <v>1580</v>
+        <v>515</v>
       </c>
       <c r="O27" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Stella Rosa Rosso 750ml</t>
+          <t>Stella Rosa Pineapple 750ml</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>087872630139</t>
+          <t>087872638401</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -17583,95 +17715,207 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106</v>
+        <v>5</v>
       </c>
       <c r="F28" t="n">
-        <v>12.6</v>
+        <v>7.1</v>
       </c>
       <c r="G28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>7</v>
+        <v>0.8</v>
       </c>
       <c r="I28" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>12</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
         <v>8</v>
       </c>
-      <c r="K28" t="n">
-        <v>84</v>
-      </c>
-      <c r="L28" t="n">
-        <v>7</v>
-      </c>
-      <c r="M28" t="n">
-        <v>8.470000000000001</v>
-      </c>
       <c r="N28" t="n">
-        <v>712</v>
+        <v>96</v>
       </c>
       <c r="O28" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Stella Rosa Red 750ml</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>087872633406</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Flavored</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>137</v>
+      </c>
+      <c r="F29" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>12</v>
+      </c>
+      <c r="H29" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="I29" t="n">
+        <v>8</v>
+      </c>
+      <c r="J29" t="n">
+        <v>4</v>
+      </c>
+      <c r="K29" t="n">
+        <v>168</v>
+      </c>
+      <c r="L29" t="n">
+        <v>14</v>
+      </c>
+      <c r="M29" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1580</v>
+      </c>
+      <c r="O29" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Stella Rosa Rosso 750ml</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>087872630139</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Flavored</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>106</v>
+      </c>
+      <c r="F30" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="G30" t="n">
+        <v>5</v>
+      </c>
+      <c r="H30" t="n">
+        <v>7</v>
+      </c>
+      <c r="I30" t="n">
+        <v>9</v>
+      </c>
+      <c r="J30" t="n">
+        <v>8</v>
+      </c>
+      <c r="K30" t="n">
+        <v>84</v>
+      </c>
+      <c r="L30" t="n">
+        <v>7</v>
+      </c>
+      <c r="M30" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="N30" t="n">
+        <v>712</v>
+      </c>
+      <c r="O30" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Stella Rosa Tropical Mango 750ml</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>087872633956</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Flavored</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
-      <c r="E29" t="n">
+      <c r="E31" t="n">
         <v>8</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F31" t="n">
         <v>3.1</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G31" t="n">
         <v>65</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H31" t="n">
         <v>0.5</v>
       </c>
-      <c r="I29" t="n">
+      <c r="I31" t="n">
         <v>3</v>
       </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
         <v>48</v>
       </c>
-      <c r="L29" t="n">
+      <c r="L31" t="n">
         <v>4</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M31" t="n">
         <v>8.470000000000001</v>
       </c>
-      <c r="N29" t="n">
+      <c r="N31" t="n">
         <v>406</v>
       </c>
-      <c r="O29" t="n">
+      <c r="O31" t="n">
         <v>44</v>
       </c>
-      <c r="Q29" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Wine Recommended Order.xlsx
+++ b/data/Wine Recommended Order.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4944,25 +4944,21 @@
         <v>73</v>
       </c>
       <c r="K76" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="L76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M76" t="n">
         <v>6.89</v>
       </c>
       <c r="N76" t="n">
-        <v>248</v>
+        <v>83</v>
       </c>
       <c r="O76" t="n">
         <v>67</v>
       </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>ON AD - Sunday special (buy to 4.5w)</t>
-        </is>
-      </c>
+      <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr"/>
     </row>
@@ -19891,7 +19887,11 @@
       <c r="O9" t="n">
         <v>52</v>
       </c>
-      <c r="Q9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>ON AD - Sunday special (buy to 4.5w)</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr">
         <is>
           <t>Wait for buy-month (Apr, Jun)</t>
